--- a/02_DIA_inicio_2026_analisis_assets/rbd_9614_escuela-basica-karelmapu_nt2_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9614_escuela-basica-karelmapu_nt2_nucleos.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D4876A0-7F1F-4FDA-A5F2-EC43F95642CF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B0CBEA23-4582-4ACD-823A-CBF838169A1E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B60D5782-CF91-4262-8E56-4B9F4F428B8D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F38E6AA1-8391-4D19-98D0-A0CF86C44AF9}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C5619139-72B3-44EE-87DB-939E346535B7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F4E01DC-8BAB-4447-AF53-C2C09B6658C5}"/>
 </file>